--- a/Configs/GameConfig/Datas/Items.xlsx
+++ b/Configs/GameConfig/Datas/Items.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EquipmentConfig" sheetId="1" r:id="R5f061303455942b2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EquipmentDropPoolConfig" sheetId="2" r:id="R804224742e884228"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupConfig" sheetId="3" r:id="Ra9c064d3af024ed7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EquipmentConfig" sheetId="1" r:id="R6629edd7f9fa4f3e"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EquipmentDropPoolConfig" sheetId="2" r:id="Ra3fd1d82fcff42c7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupConfig" sheetId="3" r:id="Rc251a019e1304f8f"/>
   </sheets>
 </workbook>
 </file>
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="200" formatCode="0%"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -41,11 +44,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -880,20 +884,44 @@
       <c r="T15"/>
       <c r="U15"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="72" customHeight="1">
       <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
+      <c r="B16" t="str">
+        <v>地煞灵戒</v>
+      </c>
+      <c r="C16" t="str">
+        <v>dslj</v>
+      </c>
+      <c r="D16" t="str">
+        <v>地煞灵戒</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <v>聚万物之灵气，佩戴后来去通风，聆其音，知其前后，万物皆明</v>
+      </c>
+      <c r="F16" t="str">
+        <v>通用</v>
+      </c>
+      <c r="G16" t="str">
+        <v>饰品</v>
+      </c>
+      <c r="H16" t="str">
+        <v>优秀</v>
+      </c>
+      <c r="I16" t="n">
+        <v>40</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Power</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15</v>
+      </c>
       <c r="N16"/>
       <c r="O16"/>
       <c r="P16"/>
@@ -903,20 +931,28 @@
       <c r="T16"/>
       <c r="U16"/>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
-      <c r="E17"/>
+      <c r="E17" s="1"/>
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
+      <c r="J17" t="str">
+        <v>Def</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
       <c r="N17"/>
       <c r="O17"/>
       <c r="P17"/>
@@ -926,20 +962,28 @@
       <c r="T17"/>
       <c r="U17"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
-      <c r="E18"/>
+      <c r="E18" s="1"/>
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18"/>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
+      <c r="J18" t="str">
+        <v>Crit</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0.03</v>
+      </c>
       <c r="N18"/>
       <c r="O18"/>
       <c r="P18"/>
@@ -949,20 +993,28 @@
       <c r="T18"/>
       <c r="U18"/>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
-      <c r="E19"/>
+      <c r="E19" s="1"/>
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19"/>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
+      <c r="J19" t="str">
+        <v>Miss</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0.03</v>
+      </c>
       <c r="N19"/>
       <c r="O19"/>
       <c r="P19"/>
@@ -972,20 +1024,44 @@
       <c r="T19"/>
       <c r="U19"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="72" customHeight="1">
       <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
+      <c r="B20" t="str">
+        <v>地煞猿甲</v>
+      </c>
+      <c r="C20" t="str">
+        <v>dsyj</v>
+      </c>
+      <c r="D20" t="str">
+        <v>地煞猿甲</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <v>据说是通臂猿猴的战甲，染上了无法褪去的血迹和被遗忘的记忆</v>
+      </c>
+      <c r="F20" t="str">
+        <v>悟空</v>
+      </c>
+      <c r="G20" t="str">
+        <v>防具</v>
+      </c>
+      <c r="H20" t="str">
+        <v>优秀</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40</v>
+      </c>
+      <c r="J20" t="str">
+        <v>MaxHp</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L20" t="n">
+        <v>80</v>
+      </c>
+      <c r="M20" t="n">
+        <v>110</v>
+      </c>
       <c r="N20"/>
       <c r="O20"/>
       <c r="P20"/>
@@ -995,20 +1071,28 @@
       <c r="T20"/>
       <c r="U20"/>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
-      <c r="E21"/>
+      <c r="E21" s="1"/>
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
+      <c r="J21" t="str">
+        <v>MaxMp</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L21" t="n">
+        <v>50</v>
+      </c>
+      <c r="M21" t="n">
+        <v>70</v>
+      </c>
       <c r="N21"/>
       <c r="O21"/>
       <c r="P21"/>
@@ -1018,20 +1102,28 @@
       <c r="T21"/>
       <c r="U21"/>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
-      <c r="E22"/>
+      <c r="E22" s="1"/>
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
+      <c r="J22" t="str">
+        <v>Def</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
       <c r="N22"/>
       <c r="O22"/>
       <c r="P22"/>
@@ -1041,20 +1133,44 @@
       <c r="T22"/>
       <c r="U22"/>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="72" customHeight="1">
       <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
+      <c r="B23" t="str">
+        <v>地煞权杖</v>
+      </c>
+      <c r="C23" t="str">
+        <v>dsqz</v>
+      </c>
+      <c r="D23" t="str">
+        <v>地煞权杖</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <v>权杖捆绑着上古遗骸，蕴藏驱神之力，挥舞间，兴云起雾，电闪雷鸣</v>
+      </c>
+      <c r="F23" t="str">
+        <v>唐僧</v>
+      </c>
+      <c r="G23" t="str">
+        <v>武器</v>
+      </c>
+      <c r="H23" t="str">
+        <v>优秀</v>
+      </c>
+      <c r="I23" t="n">
+        <v>40</v>
+      </c>
+      <c r="J23" t="str">
+        <v>MaxMp</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L23" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" t="n">
+        <v>100</v>
+      </c>
       <c r="N23"/>
       <c r="O23"/>
       <c r="P23"/>
@@ -1064,20 +1180,28 @@
       <c r="T23"/>
       <c r="U23"/>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24" ht="28" customHeight="1">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
-      <c r="E24"/>
+      <c r="E24" s="1"/>
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
+      <c r="J24" t="str">
+        <v>Power</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20</v>
+      </c>
       <c r="N24"/>
       <c r="O24"/>
       <c r="P24"/>
@@ -1382,6 +1506,47 @@
         <v>普通的松木杖</v>
       </c>
       <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12" t="str">
+        <v>猕猴王装备</v>
+      </c>
+      <c r="C12" t="str">
+        <v>水帘洞守关装备</v>
+      </c>
+      <c r="D12" t="str">
+        <v>地煞灵戒</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13" t="str">
+        <v>禺狨王装备</v>
+      </c>
+      <c r="C13" t="str">
+        <v>桃花源守关装备</v>
+      </c>
+      <c r="D13" t="str">
+        <v>地煞猿甲</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14" t="str">
+        <v>地煞权杖</v>
+      </c>
+      <c r="E14" t="n">
         <v>1</v>
       </c>
     </row>
